--- a/resultados/metricas/metricas_modelos_monografia.xlsx
+++ b/resultados/metricas/metricas_modelos_monografia.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metricas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metricas'!$A$1:$S$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metricas'!$A$1:$S$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,24 +457,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -682,7 +682,7 @@
         <v>0.157689559348948</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.211044730413968</v>
+        <v>0.2643999014789881</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2516595171378183</v>
@@ -749,7 +749,7 @@
         <v>0.06637554585152838</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.05621412729646122</v>
+        <v>0.06637554585152838</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0.01144470381303009</v>
@@ -787,63 +787,63 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FairShap</t>
+          <t>FAGTB</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>FairShap</t>
+          <t>FAGTB</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Branco|P=1</t>
+          <t>Preto|P=0</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.6445164775796867</v>
+        <v>0.5948136142625607</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.6650943396226415</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.6994047619047619</v>
+        <v>0.5849802371541502</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.8809523809523809</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.2334943639291465</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.198991182931815</v>
+        <v>0.7030878859857482</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.002096069868995576</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.0140920233166395</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1673011199326989</v>
+        <v>0.01206570705487753</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.88</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.789049919484702</v>
+        <v>0.8820960698689956</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.3013100436681223</v>
+        <v>0.7388724035608308</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.4657980456026058</v>
+        <v>0.7529644268774703</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.461038961038961</v>
+        <v>0.826381059751973</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6283400809716599</v>
+        <v>0.8143153526970954</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.6282467532467533</v>
+        <v>0.6200676437429538</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5028340080971659</v>
+        <v>0.475103734439834</v>
       </c>
     </row>
     <row r="6">
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FAGTB</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FAGTB</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -867,44 +867,44 @@
           <t>Preto|P=0</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0.5915721231766613</v>
+      <c r="E6" s="4" t="n">
+        <v>0.6645056726094003</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.5759036144578313</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0.9484126984126984</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.7166416791604198</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0.002508932115919071</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0.02490244109930317</v>
+        <v>0.6698858647936786</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.7107591988821611</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.0340214370782056</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.04098004949507983</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.0357772715152479</v>
+        <v>0.04501513329933993</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.9472727272727273</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9497816593886463</v>
+        <v>0.7794759825327511</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.8635014836795252</v>
+        <v>0.4718100890207715</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.8162055335968379</v>
+        <v>0.4308300395256917</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.915445321307779</v>
+        <v>0.6414881623449831</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.8796680497925311</v>
+        <v>0.5964730290456431</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.6200676437429538</v>
@@ -916,84 +916,84 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>COMPAS</t>
+          <t>HMDA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FAGTB</t>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>FAGTB</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Branco|P=1</t>
+          <t>Preto|P=0</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.6115613182063749</v>
+        <v>0.7779402415766052</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5915136162127929</v>
+        <v>0.7779402415766052</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9265873015873016</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.7220718979512949</v>
+        <v>0.8751027997282511</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.006665917687151302</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.06864311630485043</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06939113518060891</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.9224806201550387</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.92914653784219</v>
+        <v>1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.8602620087336245</v>
+        <v>1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.7296416938110749</v>
+        <v>1</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.8993506493506493</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8299595141700404</v>
+        <v>1</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.6282467532467533</v>
+        <v>0.8011768606000331</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5028340080971659</v>
+        <v>0.7014192139737991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>COMPAS</t>
+          <t>HMDA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1001,117 +1001,117 @@
           <t>Preto|P=0</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>0.6618044300378174</v>
+      <c r="E8" s="3" t="n">
+        <v>0.8537190082644628</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6684303350970018</v>
+        <v>0.8532423208191127</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.751984126984127</v>
+        <v>0.9806325079676391</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.707749766573296</v>
+        <v>0.912512832211703</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.04311234616911475</v>
+        <v>0.02867897886789628</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.0326515156210043</v>
+        <v>0.04849903181779736</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.0316664873436967</v>
+        <v>0.07256160983585913</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.7363636363636363</v>
+        <v>0.9866556325643944</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.7794759825327511</v>
+        <v>0.9579766536964981</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.456973293768546</v>
+        <v>0.60608586911213</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5575868372943327</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.6302142051860203</v>
+        <v>0.9109895574341124</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.5985477178423236</v>
+        <v>0.8384279475982532</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.6200676437429538</v>
+        <v>0.8011768606000331</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.475103734439834</v>
+        <v>0.7014192139737991</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>COMPAS</t>
+          <t>HMDA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>FairShap</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>FairShap</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Branco|P=1</t>
+          <t>Preto|P=0</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.6569421934089681</v>
+        <v>0.8514939605848697</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.6342692584593232</v>
+        <v>0.8511241932051918</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8740079365079365</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.7350855235711306</v>
+        <v>0.9806325079676391</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.9113001215066828</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.006740815638692332</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0.04860318593692292</v>
+        <v>0.01587268492150473</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.01783726156465248</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.07562831904937173</v>
+        <v>0.05411412630821599</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.8811369509043928</v>
+        <v>0.9839660701355125</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.8743961352657005</v>
+        <v>0.9680933852140078</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.6637554585152838</v>
+        <v>0.6065027094622759</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.5732899022801303</v>
+        <v>0.5886654478976234</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.8003246753246753</v>
+        <v>0.9089176197579977</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.7246963562753036</v>
+        <v>0.8548034934497817</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.6282467532467533</v>
+        <v>0.8011768606000331</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5028340080971659</v>
+        <v>0.7014192139737991</v>
       </c>
     </row>
     <row r="10">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Nulo</t>
+          <t>FAGTB</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>FAGTB</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1135,50 +1135,50 @@
           <t>Preto|P=0</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0.7836</v>
+      <c r="E10" s="4" t="n">
+        <v>0.8518753973299428</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7836</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0.8786723480601032</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.8511875221552641</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.981122824221623</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.911548098094298</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.002716087745263551</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.08198152338001896</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.0140498184294966</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1</v>
+        <v>0.9805523947450088</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1</v>
+        <v>0.9832684824902723</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1</v>
+        <v>0.5752396832013339</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1</v>
+        <v>0.6572212065813529</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1</v>
+        <v>0.8999668489971822</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1</v>
+        <v>0.8859170305676856</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.8051745094634485</v>
+        <v>0.8011768606000331</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7122343480758185</v>
+        <v>0.7014192139737991</v>
       </c>
     </row>
     <row r="11">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1203,455 +1203,53 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.8542666666666666</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.8535323677209578</v>
+        <v>0.7900190718372536</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.8989817792068596</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.9826442062276671</v>
+        <v>0.8225055160578573</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.9135489994463339</v>
+        <v>0.8590449366278325</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.02093156726749079</v>
+        <v>0.005683340853535612</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03776412812124097</v>
+        <v>0.02157053555983485</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.06404140900155875</v>
+        <v>0.04770215778284936</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.9870605995255554</v>
+        <v>0.821247543188166</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.9661290322580646</v>
+        <v>0.8155642023346303</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.6274509803921569</v>
+        <v>0.3184660275114631</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.5728542914171657</v>
+        <v>0.340036563071298</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.9169994790762285</v>
+        <v>0.7212829438090502</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.8529580700746697</v>
+        <v>0.6735807860262009</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.8051745094634485</v>
+        <v>0.8011768606000331</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.7122343480758185</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HMDA</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>FairShap</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>FairShap</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Preto|P=0</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.8544</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0.8527200353825741</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0.9841755997958141</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0.9137440758293839</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0.01162928617640713</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.02368531884898151</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.05203283445465423</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.9866292861764071</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>0.6265597147950089</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>0.5908183632734531</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.9164785553047404</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>0.8644457208500862</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>0.8051745094634485</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>0.7122343480758185</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HMDA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>FairShap</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>FairShap</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Branco|P=1</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.8516</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.8514311006196518</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.9819635868640463</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0.9120505728960885</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0.003344068040140868</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.0130073603778183</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.03789567616414435</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0.9835129993658845</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0.9801689313257437</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>0.6337817638266069</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0.9223123201674078</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>0.8844166440032635</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>0.8250065393669893</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>0.7405493608920315</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HMDA</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>FAGTB</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>FAGTB</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Preto|P=0</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.7833333333333333</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.7835422779407842</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.9996596903181896</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0.8785046728971962</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.0004313133491481436</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.0002156566745740718</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.0003472825143253644</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.9995686866508519</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.9996527174856746</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0.8051745094634485</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>0.7122343480758185</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>HMDA</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>FAGTB</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>FAGTB</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Branco|P=1</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.7834666666666666</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.7835711428190425</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.9998298451590948</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0.8785885167464115</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0.0003170577045021883</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0.0001585288522510941</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0.0002615746795709972</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0.9996829422954978</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0.999738425320429</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>0.8250065393669893</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>0.7405493608920315</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>HMDA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Preto|P=0</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.8839064161644807</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0.8485621915943509</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0.8658737737650838</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.02017659498980851</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.01246589524058936</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0.05753100882777784</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0.8516282078930343</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0.8314516129032258</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>0.4019607843137255</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>0.3972055888223553</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0.7640215315158881</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0.7064905226881103</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0.8051745094634485</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0.7122343480758185</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>HMDA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Branco|P=1</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.7573333333333333</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.8965786901270772</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.7803301003913561</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>0.8344250363901019</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0.006397393117321126</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0.01636957960009103</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.04933119188775603</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0.7878883956880152</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0.781491002570694</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.3408071748878924</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>0.3144654088050314</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0.7096521056761705</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>0.6603209137884145</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>0.8250065393669893</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>0.7405493608920315</v>
+        <v>0.7014192139737991</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S17"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resultados/metricas/metricas_modelos_monografia.xlsx
+++ b/resultados/metricas/metricas_modelos_monografia.xlsx
@@ -474,7 +474,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -539,42 +539,42 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>TPR|P=0</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>TPR|P=1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>TPR|P=0</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>FPR|P=0</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>FPR|P=1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>FPR|P=0</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>PR|P=0</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>PR|P=1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>PR|P=0</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>AR|P=0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>AR|P=1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>AR|P=0</t>
         </is>
       </c>
     </row>
@@ -868,43 +868,43 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.6645056726094003</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.6698858647936786</v>
+        <v>0.6704446381865736</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.7628968253968254</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.7107591988821611</v>
+        <v>0.7136890951276103</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0340214370782056</v>
+        <v>0.05001984914648672</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04098004949507983</v>
+        <v>0.05001984914648672</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.04501513329933993</v>
+        <v>0.02932164459434805</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7794759825327511</v>
+        <v>0.777292576419214</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.4718100890207715</v>
+        <v>0.4629080118694362</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.4308300395256917</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.6414881623449831</v>
+        <v>0.6268320180383314</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5964730290456431</v>
+        <v>0.5975103734439834</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.6200676437429538</v>
@@ -1203,43 +1203,43 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.7900190718372536</v>
+        <v>0.7904005085823268</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.8989817792068596</v>
+        <v>0.899535216303182</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8225055160578573</v>
+        <v>0.8224237966821933</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.8590449366278325</v>
+        <v>0.8592529348986125</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.005683340853535612</v>
+        <v>0.01328890175127462</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.02157053555983485</v>
+        <v>0.03582350354695324</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.04770215778284936</v>
+        <v>0.05079291878655745</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.821247543188166</v>
+        <v>0.8280748939691734</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.8155642023346303</v>
+        <v>0.8147859922178988</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.3184660275114631</v>
+        <v>0.3051271363067945</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.340036563071298</v>
+        <v>0.3409506398537477</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.7212829438090502</v>
+        <v>0.7241007790485662</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.6735807860262009</v>
+        <v>0.6733078602620087</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>0.8011768606000331</v>
